--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487850_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487850_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.5083</v>
+        <v>7.9665</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6066</v>
+        <v>4.386</v>
       </c>
       <c r="F2" t="n">
-        <v>4.9017</v>
+        <v>3.5805</v>
       </c>
       <c r="G2" t="n">
         <v>5.2942</v>
@@ -610,13 +610,13 @@
         <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5897</v>
+        <v>2.0479</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1365</v>
+        <v>0.9159</v>
       </c>
       <c r="U2" t="n">
-        <v>2.4532</v>
+        <v>1.132</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7289</v>
+        <v>3.8029</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4225</v>
+        <v>1.702</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3064</v>
+        <v>2.1009</v>
       </c>
       <c r="G3" t="n">
         <v>2.3969</v>
@@ -688,13 +688,13 @@
         <v>0.4162</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2518</v>
+        <v>-0.1778</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9786</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7268</v>
+        <v>0.5213</v>
       </c>
       <c r="V3" t="n">
         <v>1.1675</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9225</v>
+        <v>3.3198</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3917</v>
+        <v>1.7009</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5309</v>
+        <v>1.619</v>
       </c>
       <c r="G4" t="n">
         <v>2.8262</v>
@@ -766,13 +766,13 @@
         <v>1.4568</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3823</v>
+        <v>1.015</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5872000000000001</v>
+        <v>0.722</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2049</v>
+        <v>0.293</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9376</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9074</v>
+        <v>2.3375</v>
       </c>
       <c r="E5" t="n">
-        <v>1.78</v>
+        <v>1.8871</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1274</v>
+        <v>0.4504</v>
       </c>
       <c r="G5" t="n">
         <v>4.9937</v>
@@ -844,13 +844,13 @@
         <v>0.4162</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2944</v>
+        <v>-0.8643</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1091</v>
+        <v>-1.002</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1852</v>
+        <v>0.1377</v>
       </c>
       <c r="V5" t="n">
         <v>-1.1675</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1044</v>
+        <v>1.3126</v>
       </c>
       <c r="E6" t="n">
-        <v>0.607</v>
+        <v>0.8447</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4973</v>
+        <v>0.468</v>
       </c>
       <c r="G6" t="n">
         <v>0.0304</v>
@@ -922,13 +922,13 @@
         <v>1.4568</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2415</v>
+        <v>1.4498</v>
       </c>
       <c r="T6" t="n">
-        <v>0.972</v>
+        <v>1.2097</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2695</v>
+        <v>0.2401</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5838</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. MENDIOLA DIEZ</t>
+          <t>G. VILLAREJO COSTA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4228</v>
+        <v>-0.9441000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8701</v>
+        <v>-1.2329</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4473</v>
+        <v>0.2888</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3154</v>
+        <v>1.0458</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4395</v>
+        <v>0.062</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1241</v>
+        <v>0.9838</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5155</v>
+        <v>0.3111</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9579</v>
+        <v>0.1151</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5576</v>
+        <v>0.1959</v>
       </c>
       <c r="M7" t="n">
-        <v>1.2001</v>
+        <v>0.7347</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5183</v>
+        <v>-0.0532</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6817</v>
+        <v>0.7879</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.4568</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="S7" t="n">
-        <v>2.0571</v>
+        <v>-0.198</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5153</v>
+        <v>-0.5034</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5417</v>
+        <v>0.3054</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7076</v>
+        <v>-1.1675</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2112</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.9188</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9536</v>
+        <v>-0.9478</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.047</v>
+        <v>-1.4523</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0935</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>-0.08160000000000001</v>
@@ -1078,13 +1078,13 @@
         <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7117</v>
+        <v>0.7175</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1645</v>
+        <v>0.7592</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4527</v>
+        <v>-0.0417</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1675</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. VILLAREJO COSTA</t>
+          <t>L. GARCIA MUÑOZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3639</v>
+        <v>-1.0275</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4472</v>
+        <v>-1.2856</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0833</v>
+        <v>0.2581</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0458</v>
+        <v>-0.4103</v>
       </c>
       <c r="H9" t="n">
-        <v>0.062</v>
+        <v>-1.0789</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9838</v>
+        <v>0.6686</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3111</v>
+        <v>-0.6591</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1151</v>
+        <v>-1.1114</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1959</v>
+        <v>0.4523</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7347</v>
+        <v>0.2488</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0532</v>
+        <v>0.0324</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7879</v>
+        <v>0.2164</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6244</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4162</v>
+        <v>1.6649</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6178</v>
+        <v>1.4234</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7177</v>
+        <v>1.0978</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0998</v>
+        <v>0.3256</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1675</v>
+        <v>-0.5838</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1675</v>
+        <v>-1.9813</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. GARCIA MUÑOZ</t>
+          <t>S. MENDIOLA DIEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9786</v>
+        <v>-1.7498</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7375</v>
+        <v>-1.7274</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.241</v>
+        <v>-0.0224</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4103</v>
+        <v>-0.3154</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0789</v>
+        <v>-0.4395</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6686</v>
+        <v>0.1241</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6591</v>
+        <v>-1.5155</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1114</v>
+        <v>-0.9579</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4523</v>
+        <v>-0.5576</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2488</v>
+        <v>1.2001</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0324</v>
+        <v>0.5183</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2164</v>
+        <v>0.6817</v>
       </c>
       <c r="P10" t="n">
         <v>-1.4568</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1218</v>
+        <v>-2.0812</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4723</v>
+        <v>0.7301</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6458</v>
+        <v>-0.3419</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1735</v>
+        <v>1.072</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5838</v>
+        <v>-0.7076</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3975</v>
+        <v>2.2112</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.9813</v>
+        <v>-2.9188</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.346</v>
+        <v>-2.3111</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8485</v>
+        <v>-1.3128</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4974</v>
+        <v>-0.9983</v>
       </c>
       <c r="G11" t="n">
         <v>3.0193</v>
@@ -1312,13 +1312,13 @@
         <v>0.6244</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3851</v>
+        <v>-0.3502</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5006</v>
+        <v>-0.9648</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1155</v>
+        <v>0.6146</v>
       </c>
       <c r="V11" t="n">
         <v>-4.564</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11.1066</v>
+        <v>11.759</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8575</v>
+        <v>3.5097</v>
       </c>
       <c r="F12" t="n">
-        <v>8.2494</v>
+        <v>8.249499999999999</v>
       </c>
       <c r="G12" t="n">
         <v>18.7992</v>
@@ -1360,7 +1360,7 @@
         <v>12.2065</v>
       </c>
       <c r="I12" t="n">
-        <v>6.592499999999998</v>
+        <v>6.592499999999999</v>
       </c>
       <c r="J12" t="n">
         <v>11.0857</v>
@@ -1369,7 +1369,7 @@
         <v>10.412</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6734000000000008</v>
+        <v>0.6734000000000007</v>
       </c>
       <c r="M12" t="n">
         <v>7.7136</v>
@@ -1390,10 +1390,10 @@
         <v>10.4057</v>
       </c>
       <c r="S12" t="n">
-        <v>5.1409</v>
+        <v>5.793400000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5408999999999997</v>
+        <v>1.1934</v>
       </c>
       <c r="U12" t="n">
         <v>4.6</v>
@@ -1402,7 +1402,7 @@
         <v>-9.7118</v>
       </c>
       <c r="W12" t="n">
-        <v>4.758599999999999</v>
+        <v>4.7586</v>
       </c>
       <c r="X12" t="n">
         <v>-14.4703</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.7784</v>
+        <v>2.2617</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1214</v>
+        <v>2.6928</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.343</v>
+        <v>-0.4311</v>
       </c>
       <c r="G13" t="n">
         <v>0.09180000000000001</v>
@@ -1468,13 +1468,13 @@
         <v>1.0406</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7085</v>
+        <v>0.1918</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3353</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3732</v>
+        <v>0.2851</v>
       </c>
       <c r="V13" t="n">
         <v>0.9376</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7858</v>
+        <v>0.9329</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4876</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2983</v>
+        <v>0.1239</v>
       </c>
       <c r="G15" t="n">
         <v>2.1302</v>
@@ -1624,13 +1624,13 @@
         <v>1.2487</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4881</v>
+        <v>-0.3648</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.162</v>
+        <v>-0.8405</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6501</v>
+        <v>0.4757</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. OCHI</t>
+          <t>A. BOUZAN CUMPLIDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2802</v>
+        <v>-0.8778</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4013</v>
+        <v>-1.4691</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1211</v>
+        <v>0.5914</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.0224</v>
+        <v>-1.4594</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.6762</v>
+        <v>0.064</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3462</v>
+        <v>-1.5234</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.1443</v>
+        <v>-1.292</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.794</v>
+        <v>0.0192</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.3504</v>
+        <v>-1.3112</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.878</v>
+        <v>-0.1674</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8823</v>
+        <v>0.0449</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0042</v>
+        <v>-0.2123</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2081</v>
+        <v>0.4162</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2487</v>
+        <v>0.4162</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0518</v>
+        <v>0.1654</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0837</v>
+        <v>-0.1771</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0319</v>
+        <v>0.3425</v>
       </c>
       <c r="V16" t="n">
-        <v>3.0427</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.5026</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BOUZAN CUMPLIDO</t>
+          <t>J. HANNA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2976</v>
+        <v>-1.5303</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6835</v>
+        <v>-1.6521</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3858</v>
+        <v>0.1218</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4594</v>
+        <v>-1.2485</v>
       </c>
       <c r="H17" t="n">
-        <v>0.064</v>
+        <v>-1.7482</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5234</v>
+        <v>0.4997</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.292</v>
+        <v>0.352</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0192</v>
+        <v>-0.3926</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3112</v>
+        <v>0.7446</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1674</v>
+        <v>-1.6005</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0449</v>
+        <v>-1.3556</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2123</v>
+        <v>-0.2449</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4162</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4162</v>
+        <v>1.8731</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2544</v>
+        <v>-0.7813</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3915</v>
+        <v>-0.5067</v>
       </c>
       <c r="U17" t="n">
-        <v>0.137</v>
+        <v>-0.2746</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.7076</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.1238</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. HANNA</t>
+          <t>M. OCHI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3494</v>
+        <v>-1.8835</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.295</v>
+        <v>-1.5275</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0544</v>
+        <v>-0.356</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2485</v>
+        <v>-5.0224</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7482</v>
+        <v>-4.6762</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4997</v>
+        <v>-0.3462</v>
       </c>
       <c r="J18" t="n">
-        <v>0.352</v>
+        <v>-4.1443</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3926</v>
+        <v>-2.794</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7446</v>
+        <v>-1.3504</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6005</v>
+        <v>-0.878</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3556</v>
+        <v>-1.8823</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2449</v>
+        <v>1.0042</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2081</v>
+        <v>0.2081</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8731</v>
+        <v>1.2487</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6004</v>
+        <v>-0.1119</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1496</v>
+        <v>0.1549</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4508</v>
+        <v>-0.2668</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7076</v>
+        <v>3.0427</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5838</v>
+        <v>3.5026</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1238</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4926</v>
+        <v>-2.2386</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7896</v>
+        <v>-1.6824</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.703</v>
+        <v>-0.5562</v>
       </c>
       <c r="G19" t="n">
         <v>-2.0807</v>
@@ -1936,13 +1936,13 @@
         <v>0.4162</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-0.7012</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6524</v>
+        <v>-0.5453</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3027</v>
+        <v>-0.1559</v>
       </c>
       <c r="V19" t="n">
         <v>1.1675</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. MARIN FONTAN</t>
+          <t>P. ISERN MAZA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0574</v>
+        <v>-2.4726</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.741</v>
+        <v>-1.7465</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3165</v>
+        <v>-0.726</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.9604</v>
+        <v>-2.965</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.0616</v>
+        <v>-2.578</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8989</v>
+        <v>-0.387</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.1558</v>
+        <v>-1.6543</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.8937</v>
+        <v>-1.2265</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2621</v>
+        <v>-0.4278</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8047</v>
+        <v>-1.3106</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1679</v>
+        <v>-1.3515</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6368</v>
+        <v>0.0408</v>
       </c>
       <c r="P20" t="n">
-        <v>1.2487</v>
+        <v>0.4162</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2893</v>
+        <v>1.4568</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.2208</v>
+        <v>-0.1538</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0472</v>
+        <v>-0.6791</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1736</v>
+        <v>0.5252</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8751</v>
+        <v>0.23</v>
       </c>
       <c r="W20" t="n">
-        <v>3.5026</v>
+        <v>1.6275</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.6275</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. ISERN MAZA</t>
+          <t>P. MARIN FONTAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1258</v>
+        <v>-2.6655</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2823</v>
+        <v>-0.8481</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8435</v>
+        <v>-1.8174</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.965</v>
+        <v>-3.9604</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.578</v>
+        <v>-3.0616</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.387</v>
+        <v>-0.8989</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6543</v>
+        <v>-2.1558</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2265</v>
+        <v>-1.8937</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.4278</v>
+        <v>-0.2621</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3106</v>
+        <v>-1.8047</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3515</v>
+        <v>-1.1679</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0408</v>
+        <v>-0.6368</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4568</v>
+        <v>2.2893</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-1.8289</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2148</v>
+        <v>-1.1543</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4078</v>
+        <v>-0.6745</v>
       </c>
       <c r="V21" t="n">
-        <v>0.23</v>
+        <v>1.8751</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6275</v>
+        <v>3.5026</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3975</v>
+        <v>-1.6275</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.4562</v>
+        <v>-4.461</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.09</v>
+        <v>-4.4471</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3662</v>
+        <v>-0.0139</v>
       </c>
       <c r="G22" t="n">
         <v>-3.3332</v>
@@ -2170,13 +2170,13 @@
         <v>1.6649</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.2906</v>
+        <v>-1.2954</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0191</v>
+        <v>-0.3762</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.2715</v>
+        <v>-0.9192</v>
       </c>
       <c r="V22" t="n">
         <v>0.5838</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-11.1066</v>
+        <v>-11.1067</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.249300000000002</v>
+        <v>-8.249199999999998</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8574</v>
+        <v>-2.8573</v>
       </c>
       <c r="G23" t="n">
         <v>-18.7992</v>
@@ -2221,10 +2221,10 @@
         <v>-6.592600000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-7.7136</v>
+        <v>-7.713600000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.7944</v>
+        <v>-1.794399999999999</v>
       </c>
       <c r="L23" t="n">
         <v>-5.9193</v>
@@ -2236,7 +2236,7 @@
         <v>-10.4122</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6734000000000002</v>
+        <v>-0.6734</v>
       </c>
       <c r="P23" t="n">
         <v>3.1217</v>
@@ -2248,13 +2248,13 @@
         <v>13.5276</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.140899999999999</v>
+        <v>-5.1411</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.6</v>
+        <v>-4.600000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5409999999999999</v>
+        <v>-0.5411</v>
       </c>
       <c r="V23" t="n">
         <v>9.7118</v>
